--- a/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>REVG</t>
   </si>
@@ -656,403 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>586000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>693300</v>
+      </c>
+      <c r="F8" s="3">
         <v>680000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>681200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>583500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>623500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>594800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>576300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>537000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>589900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>593300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>643600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>554000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>616300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>582200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>547000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>532100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>652900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>617000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>615000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>518700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>659900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>597700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>608900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>514900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>683900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>595600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>545300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>442900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>544800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>523100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>597800</v>
+      </c>
+      <c r="F9" s="3">
         <v>599800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>598700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>525600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>556700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>527000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>519200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>481200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>524600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>516700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>556200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>492300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>554500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>515700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>494600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>484700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>591200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>545700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>542600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>472400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>586700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>518200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>536100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>462300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>587700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>517600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>472500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>395400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>95500</v>
+      </c>
+      <c r="F10" s="3">
         <v>80200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>82500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>57900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>66800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>67800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>57100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>55800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>65300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>76600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>87400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>61700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>61800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>66500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>52400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>47400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>61700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>71300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>72400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>46300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>73200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>79500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>72800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>52600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>96200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>78000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>72800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>47500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,19 +1110,21 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="3">
         <v>1300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>900</v>
       </c>
       <c r="G12" s="3">
         <v>1300</v>
@@ -1105,76 +1133,82 @@
         <v>900</v>
       </c>
       <c r="I12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>900</v>
+      </c>
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1100</v>
       </c>
       <c r="T12" s="3">
         <v>1200</v>
       </c>
       <c r="U12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X12" s="3">
         <v>1300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>900</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>1000</v>
       </c>
       <c r="AD12" s="3">
         <v>1200</v>
       </c>
       <c r="AE12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,97 +1296,109 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-244100</v>
       </c>
       <c r="E14" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>200</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>5200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>17400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>8300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>3000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>7600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>3800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>35900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>1900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>4100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>2300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>12300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1360,88 +1406,94 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>500</v>
+      </c>
+      <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>2300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>3000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>3400</v>
-      </c>
-      <c r="R15" s="3">
-        <v>4000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>4000</v>
       </c>
       <c r="T15" s="3">
         <v>4000</v>
       </c>
       <c r="U15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W15" s="3">
         <v>4600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>4600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>4500</v>
       </c>
       <c r="X15" s="3">
         <v>4600</v>
       </c>
       <c r="Y15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AA15" s="3">
         <v>4300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>4700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>4500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>5100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>2700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>2600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>648200</v>
+      </c>
+      <c r="F17" s="3">
         <v>654300</v>
       </c>
-      <c r="E17" s="3">
-        <v>653300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>594800</v>
-      </c>
       <c r="G17" s="3">
+        <v>653800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>595000</v>
+      </c>
+      <c r="I17" s="3">
         <v>605500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>577600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>575500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>536100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>579100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>563800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>610300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>548500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>623500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>580600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>557400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>536800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>657900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>601100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>598900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>529900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>678300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>568800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>592500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>513900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>642700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>566800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>531000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>456600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>518500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>45100</v>
+      </c>
+      <c r="F18" s="3">
         <v>25700</v>
       </c>
-      <c r="E18" s="3">
-        <v>27900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-11300</v>
-      </c>
       <c r="G18" s="3">
+        <v>27400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="I18" s="3">
         <v>18000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>17200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>29500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>33300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-7200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-10400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>15900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>16100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-11200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-18400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>28900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>16400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>41200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>28800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>14300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-13700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1681,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1690,32 +1758,32 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-6200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1770,364 +1838,394 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>257500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>51600</v>
+      </c>
+      <c r="F21" s="3">
         <v>32000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>33900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>24900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>24100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>9500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>10500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>12400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>37000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>41400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>14100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>10800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>6100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>5900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>26900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>27500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-6300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>40700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>27500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>12000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>52300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>40400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>22200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F22" s="3">
         <v>7300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>7400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>7100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>4300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2900</v>
       </c>
       <c r="L22" s="3">
         <v>3400</v>
       </c>
       <c r="M22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>5700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>7300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>7300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>8300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>8400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>8000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>7300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>6100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>5400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>5300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>4600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>3400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>7500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>244200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>38400</v>
+      </c>
+      <c r="F23" s="3">
         <v>18400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>20000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-18600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>12100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>26100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>27800</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-12600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-17700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-12000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-13300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>7500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>8100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-19000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-25700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>22100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>10300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>36000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>24300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>10900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F24" s="3">
         <v>3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>5800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-5100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>7200</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-6600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-4400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-4800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>5900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>13300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>9100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>4100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2215,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F26" s="3">
         <v>14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>14200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-13500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>8700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>9500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>23700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>20600</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-10200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-11100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-9800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-14600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-20900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>16200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>7400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>22700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>15200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>6800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F27" s="3">
         <v>14900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>14200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-13500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>8700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>9500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>23700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>20600</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-11100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-9400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>5600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>5600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-14600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-20900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>16200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>7400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>22700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>15200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>6800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2482,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2496,8 +2618,8 @@
       <c r="F29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>24</v>
@@ -2508,32 +2630,32 @@
       <c r="J29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="3">
-        <v>4200</v>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
+      <c r="M29" s="3">
+        <v>4200</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>3500</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>24</v>
@@ -2544,23 +2666,23 @@
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-1200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>2100</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>10400</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -2571,8 +2693,14 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2758,32 +2898,32 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>6200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2838,97 +2978,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F33" s="3">
         <v>14900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-13500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>8700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>23700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>20600</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-9400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>5600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>5600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-14600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-22100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>18300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>9400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>22700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>15200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>6800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F35" s="3">
         <v>14900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-13500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>8700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>23700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>20600</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-9400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>5600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>5600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-14600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-22100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>18300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>9400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>22700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>15200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>6800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F41" s="3">
         <v>11000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>23000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>14800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>13900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>13300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>11400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>17300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>21500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>67300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>19800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>13500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>11900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>14700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>13200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>12700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>17800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>14100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>14000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>15100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,364 +3623,394 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>223500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>226500</v>
+      </c>
+      <c r="F43" s="3">
         <v>210600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>239500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>218800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>215000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>224300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>222200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>249800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>213300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>198700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>231100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>207700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>229300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>239300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>217200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>230500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>253500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>236200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>281500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>225000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>266900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>232800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>251700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>224200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>243200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>243400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>223300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>188000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>181200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>650400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>657700</v>
+      </c>
+      <c r="F44" s="3">
         <v>644000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>654400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>671900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>629500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>599300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>562900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>527600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>481700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>519700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>532900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>533200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>537200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>572300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>594000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>532700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>513400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>557900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>536300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>529800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>514000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>531500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>483900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>486700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>452400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>457800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>417600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>341500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>325600</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F45" s="3">
         <v>41400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>21500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>27600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>23500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>38000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>33600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>25600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>52700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>46700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>38400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>27300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>34100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>57900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>91100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>22900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>38900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>51300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>40300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>45300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>50300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>24200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>14700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>14100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>13400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>14900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>18300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>16400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>988600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>933200</v>
+      </c>
+      <c r="F46" s="3">
         <v>907000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>924400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>941300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>888400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>876400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>824600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>816900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>761000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>774300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>810100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>777300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>812000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>886800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>923800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>853400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>809100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>865200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>864600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>813600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>843100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>803200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>763500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>737700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>726800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>730200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>673300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>561000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>529700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,186 +4098,204 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>188100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>196500</v>
+      </c>
+      <c r="F48" s="3">
         <v>190600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>184900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>175400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>169100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>166800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>167000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>177300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>176700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>171000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>172800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>175500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>191600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>207000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>220600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>220400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>201700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>203200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>206500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>214000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>214300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>241100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>238800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>227600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>217100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>207600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>198200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>161900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>146400</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>237700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>273000</v>
+      </c>
+      <c r="F49" s="3">
         <v>273500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>274100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>275100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>276500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>277800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>279200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>281200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>283600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>286000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>288400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>290900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>293400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>299600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>302500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>315700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>319700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>323700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>327500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>332000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>336400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>342500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>346700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>349900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>301100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>300300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>295500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>215500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4478,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F52" s="3">
         <v>8400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>9100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>9800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>10600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>11200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>15000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>16900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>17000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>21600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>21600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>15400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>15300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>16000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>16000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>16500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>16600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>14000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>14700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>15000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>14300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>16300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>9700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>9400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>9400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>8000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>8500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>3900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1421100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1410400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1379500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1392500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1401600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1344600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1332200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1285800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1292300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1238300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1252900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1292900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1259100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1312300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1409400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1462900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1406000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1347100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1406100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1413300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1374600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1408100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1403100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1358700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1324500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1254400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1246100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1175400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>942200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>889000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4837,105 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>208300</v>
+      </c>
+      <c r="F57" s="3">
         <v>192700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>185700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>187100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>163900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>159200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>144700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>137100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>116200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>129600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>137200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>128700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>169500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>175800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>193200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>187400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>200800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>211000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>196500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>163900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>218100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>167200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>188100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>144300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>217300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>170200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>140600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>111400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4702,10 +4970,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>1700</v>
@@ -4714,31 +4982,31 @@
         <v>1700</v>
       </c>
       <c r="R58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T58" s="3">
         <v>3400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1300</v>
       </c>
       <c r="X58" s="3">
         <v>1300</v>
       </c>
       <c r="Y58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="Z58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="AA58" s="3">
         <v>800</v>
@@ -4749,203 +5017,221 @@
       <c r="AC58" s="3">
         <v>800</v>
       </c>
-      <c r="AD58" s="3" t="s">
+      <c r="AD58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>568300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>348900</v>
+      </c>
+      <c r="F59" s="3">
         <v>355600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>349800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>335500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>363500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>415500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>372500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>348300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>320800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>304400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>301800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>272700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>276100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>291300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>280300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>217100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>231600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>221700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>202000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>185900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>197800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>186500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>184500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>191300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>192100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>187800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>185500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>182800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>202100</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>733300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>557200</v>
+      </c>
+      <c r="F60" s="3">
         <v>548300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>535500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>522600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>527400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>574700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>517200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>485400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>437000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>434000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>439000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>403100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>447300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>468800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>475200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>407900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>436000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>434500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>400300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>351100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>417200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>355000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>373400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>336400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>410100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>358800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>326900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>294200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>331600</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F61" s="3">
         <v>179000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>230000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>250000</v>
       </c>
       <c r="G61" s="3">
         <v>230000</v>
@@ -4954,165 +5240,177 @@
         <v>250000</v>
       </c>
       <c r="I61" s="3">
+        <v>230000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>250000</v>
+      </c>
+      <c r="K61" s="3">
         <v>243000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>256000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>215000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>250000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>306000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>330400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>340500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>388700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>440800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>458300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>376600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>416800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>460000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>470400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>420600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>440400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>368900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>371500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>229100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>299400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>280800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>336000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>191700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>205200</v>
+      </c>
+      <c r="F62" s="3">
         <v>183600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>173700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>188300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>130900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>59500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>62100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>62800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>67500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>47400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>49100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>50300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>52200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>69800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>62000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>43900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>29300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>37300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>36700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>37000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>37900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>44300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>35000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>35100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>42800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>40200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>32400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>34200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5289,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>925000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>912400</v>
+      </c>
+      <c r="F66" s="3">
         <v>910900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>939200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>960900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>888300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>884200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>822300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>804200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>719500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>731400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>794100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>783800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>840000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>927300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>978000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>910100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>842100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>889600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>898000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>859500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>876700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>839700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>777300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>743000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>682000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>698300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>640000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>664400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>52700</v>
+      </c>
+      <c r="F72" s="3">
         <v>26000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>14100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>19500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>13800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>12700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>16700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>19900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-21100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-21100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-7600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>15800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>27600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>25200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>22800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>40600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>65900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>50700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>46600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>40400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>20900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>8900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>496100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>498000</v>
+      </c>
+      <c r="F76" s="3">
         <v>468600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>453300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>440700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>456300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>448000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>463500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>488100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>518800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>521500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>498800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>475300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>472300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>482100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>484900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>495900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>505000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>516500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>515300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>515100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>531400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>563400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>581400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>581600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>572400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>547700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>535400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>277800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F81" s="3">
         <v>14900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-13500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>8700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>23700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>20600</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-9400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>5600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>5600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-14600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-22100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>18300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>9400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>22700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>15200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>6800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7002,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="E83" s="3">
         <v>6500</v>
       </c>
       <c r="F83" s="3">
-        <v>6900</v>
+        <v>6300</v>
       </c>
       <c r="G83" s="3">
-        <v>7100</v>
+        <v>6500</v>
       </c>
       <c r="H83" s="3">
         <v>6900</v>
       </c>
       <c r="I83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K83" s="3">
         <v>8700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>7500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>8100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>8600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>9300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>9200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>10900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>10800</v>
       </c>
       <c r="S83" s="3">
         <v>10900</v>
       </c>
       <c r="T83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="U83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="V83" s="3">
         <v>11000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>11400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>12400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>12100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>11800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>11100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>11000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>11000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>11500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>7900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>7400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-69700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>53100</v>
+      </c>
+      <c r="F89" s="3">
         <v>65200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>15100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>32100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>32100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>31100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>57700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>63500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>35200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>30700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>35300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-13300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>30500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>61200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-39400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>37600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>28500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-72400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>93200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-25100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>86800</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7702,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-9100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-4200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>2100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>297700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-9100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>7100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>11900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>48300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-57200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-5300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>11900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-10500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-19900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-38300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-16800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,41 +8117,43 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3000</v>
+        <v>-3100</v>
       </c>
       <c r="E96" s="3">
         <v>-3000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3100</v>
+        <v>-3000</v>
       </c>
       <c r="G96" s="3">
         <v>-3000</v>
       </c>
       <c r="H96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I96" s="3">
         <v>-3000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-3300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-3300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -7693,46 +8161,46 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-3100</v>
       </c>
       <c r="T96" s="3">
         <v>-3100</v>
       </c>
       <c r="U96" s="3">
-        <v>-3200</v>
+        <v>-3100</v>
       </c>
       <c r="V96" s="3">
         <v>-3100</v>
       </c>
       <c r="W96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AA96" s="3">
         <v>-3200</v>
       </c>
       <c r="AB96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AC96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AD96" s="3">
         <v>0</v>
@@ -7740,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8493,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-161400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-54100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-23200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>12500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-23000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-17800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-37600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>8700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-42800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-59300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-32800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-11300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-48500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-55500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-23900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>78600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-41700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-48700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-19100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>48200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-29900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>34400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>140200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>15700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>182300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>76300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-76400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-14000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-45800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>64000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-16500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>13300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-7000</v>
-      </c>
-      <c r="V102" s="3">
-        <v>1600</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-2800</v>
       </c>
       <c r="X102" s="3">
         <v>1600</v>
       </c>
       <c r="Y102" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>3700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>4300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>REVG</t>
   </si>
@@ -656,429 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42945</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42854</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42763</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>616900</v>
+      </c>
+      <c r="E8" s="3">
         <v>586000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>693300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>680000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>681200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>583500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>623500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>594800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>576300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>537000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>589900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>593300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>643600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>554000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>616300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>582200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>547000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>532100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>652900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>617000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>615000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>518700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>659900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>597700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>608900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>514900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>683900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>595600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>545300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>442900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>544800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>539600</v>
+      </c>
+      <c r="E9" s="3">
         <v>523100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>597800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>599800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>598700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>525600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>556700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>527000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>519200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>481200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>524600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>516700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>556200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>492300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>554500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>515700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>494600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>484700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>591200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>545700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>542600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>472400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>586700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>518200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>536100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>462300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>587700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>517600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>472500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>395400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E10" s="3">
         <v>62900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>95500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>80200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>82500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>57900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>57100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>55800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>76600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>87400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>61700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>61800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>66500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>52400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>47400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>61700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>71300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>46300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>73200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>79500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>72800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>52600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>96200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>78000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>72800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>47500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1300</v>
       </c>
       <c r="G12" s="3">
         <v>1300</v>
       </c>
       <c r="H12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1100</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1200</v>
       </c>
       <c r="W12" s="3">
         <v>1200</v>
       </c>
       <c r="X12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y12" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>1600</v>
       </c>
       <c r="Z12" s="3">
         <v>1600</v>
       </c>
       <c r="AA12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB12" s="3">
         <v>1500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,103 +1318,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-244100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>17400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>35900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>12300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1406,52 +1428,52 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1400</v>
       </c>
       <c r="I15" s="3">
         <v>1400</v>
       </c>
       <c r="J15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K15" s="3">
         <v>1300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2400</v>
       </c>
       <c r="M15" s="3">
         <v>2400</v>
       </c>
       <c r="N15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O15" s="3">
         <v>2300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>4000</v>
       </c>
       <c r="U15" s="3">
         <v>4000</v>
@@ -1460,40 +1482,43 @@
         <v>4000</v>
       </c>
       <c r="W15" s="3">
-        <v>4600</v>
+        <v>4000</v>
       </c>
       <c r="X15" s="3">
         <v>4600</v>
       </c>
       <c r="Y15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Z15" s="3">
         <v>4500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>592500</v>
+      </c>
+      <c r="E17" s="3">
         <v>335000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>648200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>654300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>653800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>595000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>605500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>577600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>575500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>536100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>579100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>563800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>610300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>548500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>623500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>580600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>557400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>536800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>657900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>601100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>598900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>529900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>678300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>568800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>592500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>513900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>642700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>566800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>531000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>456600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>518500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E18" s="3">
         <v>251000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>45100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>29500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>41200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>28800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-13700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1770,11 +1803,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1782,11 +1815,11 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-6200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1844,388 +1877,403 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E21" s="3">
         <v>257500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>51600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>32000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>33900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>41400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>27500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>40700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>52300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>40400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>22200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E22" s="3">
         <v>6800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>5500</v>
       </c>
       <c r="P22" s="3">
         <v>5500</v>
       </c>
       <c r="Q22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="R22" s="3">
         <v>5400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5700</v>
-      </c>
-      <c r="S22" s="3">
-        <v>7300</v>
       </c>
       <c r="T22" s="3">
         <v>7300</v>
       </c>
       <c r="U22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="V22" s="3">
         <v>8300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E23" s="3">
         <v>244200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>38400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27800</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-12600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>22100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>24300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E24" s="3">
         <v>61500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>3400</v>
       </c>
       <c r="J24" s="3">
         <v>3400</v>
       </c>
       <c r="K24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E26" s="3">
         <v>182700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20600</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9800</v>
-      </c>
-      <c r="V26" s="3">
-        <v>5600</v>
       </c>
       <c r="W26" s="3">
         <v>5600</v>
       </c>
       <c r="X26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-20900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>16200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>22700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E27" s="3">
         <v>182700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20600</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>5600</v>
       </c>
       <c r="W27" s="3">
         <v>5600</v>
       </c>
       <c r="X27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-20900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>16200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>22700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2636,11 +2696,11 @@
       <c r="L29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="3">
         <v>4200</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
@@ -2648,17 +2708,17 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>3500</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -2672,20 +2732,20 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>2100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>10400</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2910,11 +2979,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2922,11 +2991,11 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>6200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2984,103 +3053,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E33" s="3">
         <v>182700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>23700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20600</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-10200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9000</v>
-      </c>
-      <c r="V33" s="3">
-        <v>5600</v>
       </c>
       <c r="W33" s="3">
         <v>5600</v>
       </c>
       <c r="X33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-22100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>15200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E35" s="3">
         <v>182700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>23700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20600</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-10200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9000</v>
-      </c>
-      <c r="V35" s="3">
-        <v>5600</v>
       </c>
       <c r="W35" s="3">
         <v>5600</v>
       </c>
       <c r="X35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-22100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>15200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42945</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42854</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42763</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E41" s="3">
         <v>87900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>67300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>14700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>14100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>14000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,388 +3718,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E43" s="3">
         <v>223500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>226500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>210600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>239500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>218800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>215000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>224300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>222200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>249800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>213300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>198700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>231100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>207700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>229300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>239300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>217200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>230500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>253500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>236200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>281500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>225000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>266900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>232800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>251700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>224200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>243200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>243400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>223300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>188000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>181200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>630400</v>
+      </c>
+      <c r="E44" s="3">
         <v>650400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>657700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>644000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>654400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>671900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>629500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>599300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>562900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>527600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>481700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>519700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>532900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>533200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>537200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>572300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>594000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>532700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>513400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>557900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>536300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>529800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>514000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>531500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>483900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>486700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>452400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>457800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>417600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>341500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>325600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E45" s="3">
         <v>26800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>52700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>46700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>57900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>91100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>38900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>40300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>50300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>24200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>14100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>18300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>905200</v>
+      </c>
+      <c r="E46" s="3">
         <v>988600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>933200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>907000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>924400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>941300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>888400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>876400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>824600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>816900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>761000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>774300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>810100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>777300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>812000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>886800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>923800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>853400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>809100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>865200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>864600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>813600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>843100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>803200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>763500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>737700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>726800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>730200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>673300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>561000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>529700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E48" s="3">
         <v>188100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>196500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>190600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>184900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>175400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>169100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>166800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>167000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>177300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>176700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>171000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>172800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>175500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>191600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>207000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>220600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>220400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>201700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>203200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>206500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>214000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>214300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>241100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>238800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>227600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>217100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>207600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>198200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>161900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>146400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E49" s="3">
         <v>237700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>273000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>273500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>274100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>275100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>276500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>277800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>279200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>281200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>283600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>286000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>288400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>290900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>293400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>299600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>302500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>315700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>319700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>323700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>327500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>332000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>336400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>342500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>346700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>349900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>301100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>300300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>295500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>215500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E52" s="3">
         <v>6700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>21600</v>
       </c>
       <c r="O52" s="3">
         <v>21600</v>
       </c>
       <c r="P52" s="3">
+        <v>21600</v>
+      </c>
+      <c r="Q52" s="3">
         <v>15400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15300</v>
-      </c>
-      <c r="R52" s="3">
-        <v>16000</v>
       </c>
       <c r="S52" s="3">
         <v>16000</v>
       </c>
       <c r="T52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="U52" s="3">
         <v>16500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9700</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>9400</v>
       </c>
       <c r="AC52" s="3">
         <v>9400</v>
       </c>
       <c r="AD52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AE52" s="3">
         <v>8000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1330400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1421100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1410400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1379500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1392500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1401600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1344600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1332200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1285800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1292300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1238300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1252900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1292900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1259100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1312300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1409400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1462900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1406000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1347100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1406100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1413300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1374600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1408100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1358700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1324500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1254400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1246100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1175400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>942200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>889000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>190200</v>
+      </c>
+      <c r="E57" s="3">
         <v>165000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>208300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>192700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>185700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>187100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>163900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>159200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>144700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>137100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>129600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>137200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>128700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>169500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>175800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>193200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>187400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>211000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>196500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>163900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>218100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>167200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>188100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>144300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>217300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>170200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>140600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>111400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4976,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>1700</v>
@@ -4988,19 +5121,19 @@
         <v>1700</v>
       </c>
       <c r="T58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U58" s="3">
         <v>3400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3600</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1800</v>
       </c>
       <c r="W58" s="3">
         <v>1800</v>
       </c>
       <c r="X58" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="Y58" s="3">
         <v>1300</v>
@@ -5009,7 +5142,7 @@
         <v>1300</v>
       </c>
       <c r="AA58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="AB58" s="3">
         <v>800</v>
@@ -5023,394 +5156,409 @@
       <c r="AE58" s="3">
         <v>800</v>
       </c>
-      <c r="AF58" s="3" t="s">
+      <c r="AF58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>328300</v>
+      </c>
+      <c r="E59" s="3">
         <v>568300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>348900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>355600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>349800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>335500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>363500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>415500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>372500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>348300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>320800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>304400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>301800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>272700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>276100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>291300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>280300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>217100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>231600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>221700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>202000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>185900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>197800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>186500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>184500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>191300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>192100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>187800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>185500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>182800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>202100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>518500</v>
+      </c>
+      <c r="E60" s="3">
         <v>733300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>557200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>548300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>535500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>522600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>527400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>574700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>517200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>485400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>437000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>434000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>439000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>403100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>447300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>468800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>475200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>407900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>436000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>434500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>400300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>351100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>417200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>355000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>373400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>336400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>410100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>358800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>326900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>294200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>331600</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>150000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>179000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>230000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>250000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>230000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>250000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>243000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>256000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>215000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>250000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>306000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>330400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>340500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>388700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>440800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>458300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>376600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>416800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>460000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>470400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>420600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>440400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>368900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>371500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>229100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>299400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>280800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>336000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212200</v>
+      </c>
+      <c r="E62" s="3">
         <v>191700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>205200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>183600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>173700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>188300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>130900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>59500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>62100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>49100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>50300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>52200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>69800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>62000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>43900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>36700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>37000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>44300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>35000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>35100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>42800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>40200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>32400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>34200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>950700</v>
+      </c>
+      <c r="E66" s="3">
         <v>925000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>912400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>910900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>939200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>960900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>888300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>884200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>822300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>804200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>719500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>731400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>794100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>783800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>840000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>927300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>978000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>910100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>842100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>889600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>898000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>859500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>876700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>839700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>777300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>743000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>682000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>698300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>640000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>664400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E72" s="3">
         <v>53000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>52700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-500</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-21100</v>
       </c>
       <c r="Q72" s="3">
         <v>-21100</v>
       </c>
       <c r="R72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="S72" s="3">
         <v>-11200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>27600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>25200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>65900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>50700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>40400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>379700</v>
+      </c>
+      <c r="E76" s="3">
         <v>496100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>498000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>468600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>453300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>440700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>456300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>448000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>463500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>488100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>518800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>521500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>498800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>475300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>472300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>482100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>484900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>495900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>505000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>516500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>515300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>515100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>531400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>563400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>581400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>581600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>572400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>547700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>535400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>277800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42945</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42854</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42763</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E81" s="3">
         <v>182700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>23700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20600</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-10200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9000</v>
-      </c>
-      <c r="V81" s="3">
-        <v>5600</v>
       </c>
       <c r="W81" s="3">
         <v>5600</v>
       </c>
       <c r="X81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-22100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>15200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7016,91 +7214,94 @@
         <v>6500</v>
       </c>
       <c r="F83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G83" s="3">
         <v>6300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11100</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>11000</v>
       </c>
       <c r="AC83" s="3">
         <v>11000</v>
       </c>
       <c r="AD83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AE83" s="3">
         <v>11500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-69700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>53100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>65200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>32100</v>
       </c>
       <c r="J89" s="3">
         <v>32100</v>
       </c>
       <c r="K89" s="3">
+        <v>32100</v>
+      </c>
+      <c r="L89" s="3">
         <v>31100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>63500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>30700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>61200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-39400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>28500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-72400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>93200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-25100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>86800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,65 +7923,66 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -7770,37 +7990,40 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E94" s="3">
         <v>297700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>7100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>11900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>48300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-57200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>11900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-38300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-16800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,16 +8351,17 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-182400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-3000</v>
       </c>
       <c r="F96" s="3">
         <v>-3000</v>
@@ -8137,25 +8370,25 @@
         <v>-3000</v>
       </c>
       <c r="H96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-3000</v>
       </c>
       <c r="J96" s="3">
         <v>-3000</v>
       </c>
       <c r="K96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-3300</v>
       </c>
       <c r="M96" s="3">
         <v>-3300</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -8167,13 +8400,13 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>-3200</v>
       </c>
       <c r="T96" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="U96" s="3">
         <v>-3100</v>
@@ -8182,19 +8415,19 @@
         <v>-3100</v>
       </c>
       <c r="W96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y96" s="3">
         <v>-3100</v>
       </c>
       <c r="Z96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AB96" s="3">
         <v>-3200</v>
@@ -8203,7 +8436,7 @@
         <v>-3200</v>
       </c>
       <c r="AD96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AE96" s="3">
         <v>0</v>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-161400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-54100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-23200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-42800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-59300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-32800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-48500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-55500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-23900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>78600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-41700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-48700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>48200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-29900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>34400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>140200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>182300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>76300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-76400</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E102" s="3">
         <v>66600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-45800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>64000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>REVG</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>579400</v>
+      </c>
+      <c r="E8" s="3">
         <v>616900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>586000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>693300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>680000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>681200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>583500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>623500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>594800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>576300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>537000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>589900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>593300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>643600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>554000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>616300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>582200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>547000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>532100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>652900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>617000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>615000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>518700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>659900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>597700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>608900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>514900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>683900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>595600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>545300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>442900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>544800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>501100</v>
+      </c>
+      <c r="E9" s="3">
         <v>539600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>523100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>597800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>599800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>598700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>525600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>556700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>527000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>519200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>481200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>524600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>516700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>556200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>492300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>554500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>515700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>494600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>484700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>591200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>545700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>542600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>472400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>586700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>518200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>536100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>462300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>587700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>517600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>472500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>395400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E10" s="3">
         <v>77300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>95500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>80200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>82500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>57900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>57100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>55800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>65300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>76600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>87400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>61700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>61800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>66500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>47400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>61700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>71300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>72400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>46300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>73200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>79500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>72800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>52600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>96200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>78000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>72800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>47500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1136,95 +1150,98 @@
       <c r="E12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3">
         <v>1200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1300</v>
       </c>
       <c r="H12" s="3">
         <v>1300</v>
       </c>
       <c r="I12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>1200</v>
       </c>
       <c r="X12" s="3">
         <v>1200</v>
       </c>
       <c r="Y12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z12" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>1600</v>
       </c>
       <c r="AA12" s="3">
         <v>1600</v>
       </c>
       <c r="AB12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC12" s="3">
         <v>1500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,162 +1338,168 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-244100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>17400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>35900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>12300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
       </c>
       <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1400</v>
       </c>
       <c r="J15" s="3">
         <v>1400</v>
       </c>
       <c r="K15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2400</v>
       </c>
       <c r="N15" s="3">
         <v>2400</v>
       </c>
       <c r="O15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P15" s="3">
         <v>2300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3400</v>
-      </c>
-      <c r="U15" s="3">
-        <v>4000</v>
       </c>
       <c r="V15" s="3">
         <v>4000</v>
@@ -1485,40 +1508,43 @@
         <v>4000</v>
       </c>
       <c r="X15" s="3">
-        <v>4600</v>
+        <v>4000</v>
       </c>
       <c r="Y15" s="3">
         <v>4600</v>
       </c>
       <c r="Z15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AA15" s="3">
         <v>4500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>549400</v>
+      </c>
+      <c r="E17" s="3">
         <v>592500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>335000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>648200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>654300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>653800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>595000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>605500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>577600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>575500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>536100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>579100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>563800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>610300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>548500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>623500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>580600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>557400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>536800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>657900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>601100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>598900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>529900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>678300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>568800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>592500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>513900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>642700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>566800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>531000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>456600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>518500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="3">
         <v>24400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>251000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>45100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>25700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>29500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>33300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>41200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>28800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-13700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1806,11 +1840,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1818,11 +1852,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-6200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1880,400 +1914,415 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E21" s="3">
         <v>30900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>257500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>32000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>33900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>41400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>26900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>40700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>27500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>12000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>52300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>40400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>5500</v>
       </c>
       <c r="Q22" s="3">
         <v>5500</v>
       </c>
       <c r="R22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="S22" s="3">
         <v>5400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5700</v>
-      </c>
-      <c r="T22" s="3">
-        <v>7300</v>
       </c>
       <c r="U22" s="3">
         <v>7300</v>
       </c>
       <c r="V22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="W22" s="3">
         <v>8300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E23" s="3">
         <v>17900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>244200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>27800</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-12600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>22100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>36000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>24300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>2700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>61500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3400</v>
       </c>
       <c r="K24" s="3">
         <v>3400</v>
       </c>
       <c r="L24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E26" s="3">
         <v>15200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>182700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>23700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20600</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9800</v>
-      </c>
-      <c r="W26" s="3">
-        <v>5600</v>
       </c>
       <c r="X26" s="3">
         <v>5600</v>
       </c>
       <c r="Y26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>16200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>182700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>23700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>20600</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-10200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>5600</v>
       </c>
       <c r="X27" s="3">
         <v>5600</v>
       </c>
       <c r="Y27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-20900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>16200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>15200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2699,11 +2760,11 @@
       <c r="M29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="3">
         <v>4200</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>24</v>
@@ -2711,17 +2772,17 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>3500</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2735,20 +2796,20 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>2100</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>10400</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2982,11 +3052,11 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2994,11 +3064,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>6200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>182700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>23700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>20600</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-10200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>5600</v>
       </c>
       <c r="X33" s="3">
         <v>5600</v>
       </c>
       <c r="Y33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-22100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>15200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>182700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>23700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>20600</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-10200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>5600</v>
       </c>
       <c r="X35" s="3">
         <v>5600</v>
       </c>
       <c r="Y35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-22100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>15200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E41" s="3">
         <v>38200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>87900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>67300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>14700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>17800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>14100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>15100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E43" s="3">
         <v>210600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>223500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>226500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>210600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>239500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>218800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>215000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>224300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>222200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>249800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>213300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>198700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>231100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>207700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>229300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>239300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>217200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>230500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>253500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>236200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>281500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>225000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>266900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>232800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>251700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>224200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>243200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>243400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>223300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>188000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>181200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>632300</v>
+      </c>
+      <c r="E44" s="3">
         <v>630400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>650400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>657700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>644000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>654400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>671900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>629500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>599300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>562900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>527600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>481700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>519700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>532900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>533200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>537200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>572300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>594000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>532700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>513400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>557900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>536300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>529800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>514000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>531500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>483900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>486700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>452400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>457800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>417600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>341500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>325600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E45" s="3">
         <v>26000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>52700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>57900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>91100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>38900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>51300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>45300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>50300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>24200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>14700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>14100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>13400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>14900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>18300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>16400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>914400</v>
+      </c>
+      <c r="E46" s="3">
         <v>905200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>988600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>933200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>907000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>924400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>941300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>888400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>876400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>824600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>816900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>761000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>774300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>810100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>777300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>812000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>886800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>923800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>853400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>809100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>865200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>864600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>813600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>843100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>803200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>763500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>737700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>726800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>730200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>673300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>561000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>529700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E48" s="3">
         <v>182800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>188100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>196500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>190600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>184900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>175400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>169100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>166800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>167000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>177300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>176700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>171000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>172800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>175500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>191600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>207000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>220600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>220400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>201700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>203200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>206500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>214000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>214300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>241100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>238800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>227600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>217100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>207600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>198200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>161900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>146400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>233600</v>
+      </c>
+      <c r="E49" s="3">
         <v>236000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>237700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>273000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>273500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>274100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>275100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>276500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>277800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>279200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>281200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>283600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>286000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>288400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>290900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>293400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>299600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>302500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>315700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>319700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>323700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>327500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>332000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>336400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>342500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>346700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>349900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>301100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>300300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>295500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>215500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>21600</v>
       </c>
       <c r="P52" s="3">
         <v>21600</v>
       </c>
       <c r="Q52" s="3">
+        <v>21600</v>
+      </c>
+      <c r="R52" s="3">
         <v>15400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15300</v>
-      </c>
-      <c r="S52" s="3">
-        <v>16000</v>
       </c>
       <c r="T52" s="3">
         <v>16000</v>
       </c>
       <c r="U52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="V52" s="3">
         <v>16500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9700</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>9400</v>
       </c>
       <c r="AD52" s="3">
         <v>9400</v>
       </c>
       <c r="AE52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AF52" s="3">
         <v>8000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1334700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1330400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1421100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1410400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1379500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1392500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1401600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1344600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1332200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1285800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1292300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1238300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1252900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1292900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1259100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1312300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1409400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1462900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1406000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1347100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1406100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1413300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1374600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1408100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1358700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1324500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1254400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1246100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1175400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>942200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>889000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>196600</v>
+      </c>
+      <c r="E57" s="3">
         <v>190200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>165000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>208300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>192700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>185700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>187100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>163900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>159200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>144700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>137100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>116200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>129600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>137200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>128700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>169500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>175800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>193200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>187400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>211000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>196500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>163900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>218100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>167200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>188100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>144300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>217300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>170200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>140600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>111400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5112,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>1700</v>
@@ -5124,19 +5258,19 @@
         <v>1700</v>
       </c>
       <c r="U58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V58" s="3">
         <v>3400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3600</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1800</v>
       </c>
       <c r="X58" s="3">
         <v>1800</v>
       </c>
       <c r="Y58" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="Z58" s="3">
         <v>1300</v>
@@ -5145,7 +5279,7 @@
         <v>1300</v>
       </c>
       <c r="AB58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="AC58" s="3">
         <v>800</v>
@@ -5159,406 +5293,421 @@
       <c r="AF58" s="3">
         <v>800</v>
       </c>
-      <c r="AG58" s="3" t="s">
+      <c r="AG58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>296700</v>
+      </c>
+      <c r="E59" s="3">
         <v>328300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>568300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>348900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>355600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>349800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>335500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>363500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>415500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>372500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>348300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>320800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>304400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>301800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>272700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>276100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>291300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>280300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>217100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>231600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>221700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>202000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>185900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>197800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>186500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>184500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>191300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>192100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>187800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>185500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>182800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>202100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>493300</v>
+      </c>
+      <c r="E60" s="3">
         <v>518500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>733300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>557200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>548300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>535500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>522600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>527400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>574700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>517200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>485400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>437000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>434000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>439000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>403100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>447300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>468800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>475200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>407900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>436000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>434500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>400300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>351100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>417200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>355000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>373400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>336400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>410100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>358800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>326900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>294200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>331600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E61" s="3">
         <v>220000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>150000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>179000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>230000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>250000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>230000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>250000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>243000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>256000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>215000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>250000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>306000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>330400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>340500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>388700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>440800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>458300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>376600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>416800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>460000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>470400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>420600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>440400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>368900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>371500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>229100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>299400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>280800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>336000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>231800</v>
+      </c>
+      <c r="E62" s="3">
         <v>212200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>191700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>205200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>183600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>173700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>188300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>130900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>62800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>67500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>49100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>50300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>52200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>69800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>62000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>29300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>36700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>44300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>35000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>35100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>42800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>40200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>32400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>34200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>940100</v>
+      </c>
+      <c r="E66" s="3">
         <v>950700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>925000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>912400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>910900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>939200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>960900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>888300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>884200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>822300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>804200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>719500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>731400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>794100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>783800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>840000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>927300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>978000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>910100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>842100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>889600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>898000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>859500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>876700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>839700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>777300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>743000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>682000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>698300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>640000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>664400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E72" s="3">
         <v>65100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>53000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>52700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-21100</v>
       </c>
       <c r="R72" s="3">
         <v>-21100</v>
       </c>
       <c r="S72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="T72" s="3">
         <v>-11200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>27600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>25200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>40600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>65900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>50700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>46600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>40400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>394600</v>
+      </c>
+      <c r="E76" s="3">
         <v>379700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>496100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>498000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>468600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>453300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>440700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>456300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>448000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>463500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>488100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>518800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>521500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>498800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>475300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>472300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>482100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>484900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>495900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>505000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>516500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>515300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>515100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>531400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>563400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>581400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>581600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>572400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>547700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>535400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>277800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>182700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>23700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>20600</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-10200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>5600</v>
       </c>
       <c r="X81" s="3">
         <v>5600</v>
       </c>
       <c r="Y81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-22100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>15200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="E83" s="3">
         <v>6500</v>
@@ -7217,91 +7416,94 @@
         <v>6500</v>
       </c>
       <c r="G83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H83" s="3">
         <v>6300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>11000</v>
       </c>
       <c r="AD83" s="3">
         <v>11000</v>
       </c>
       <c r="AE83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>11500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E89" s="3">
         <v>40100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-69700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>65200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>32100</v>
       </c>
       <c r="K89" s="3">
         <v>32100</v>
       </c>
       <c r="L89" s="3">
+        <v>32100</v>
+      </c>
+      <c r="M89" s="3">
         <v>31100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>63500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>35300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>30500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>61200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-39400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>28500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-72400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>93200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-25100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>86800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7933,59 +8154,59 @@
         <v>-5900</v>
       </c>
       <c r="E91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-10500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2900</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -7993,37 +8214,40 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>2100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>4200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>297700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>7100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>11900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>48300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-57200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>11900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-38300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-16800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,19 +8585,20 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-182400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-3000</v>
       </c>
       <c r="G96" s="3">
         <v>-3000</v>
@@ -8373,25 +8607,25 @@
         <v>-3000</v>
       </c>
       <c r="I96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-3000</v>
       </c>
       <c r="K96" s="3">
         <v>-3000</v>
       </c>
       <c r="L96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-3300</v>
       </c>
       <c r="N96" s="3">
         <v>-3300</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8403,13 +8637,13 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-3200</v>
       </c>
       <c r="U96" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="V96" s="3">
         <v>-3100</v>
@@ -8418,19 +8652,19 @@
         <v>-3100</v>
       </c>
       <c r="X96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z96" s="3">
         <v>-3100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AC96" s="3">
         <v>-3200</v>
@@ -8439,7 +8673,7 @@
         <v>-3200</v>
       </c>
       <c r="AE96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-94000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-161400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-23200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-42800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-59300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-48500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-55500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-23900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>78600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-41700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-48700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-19100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>48200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>34400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>140200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>15700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>182300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>76300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-76400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-49700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-45800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>64000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>REVG</t>
   </si>
@@ -1154,16 +1154,16 @@
         <v>24</v>
       </c>
       <c r="G12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>900</v>
+        <v>-3500</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K12" s="3">
         <v>1300</v>
@@ -1353,16 +1353,16 @@
         <v>2200</v>
       </c>
       <c r="F14" s="3">
-        <v>-244100</v>
+        <v>-239100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>10500</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I14" s="3">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="J14" s="3">
         <v>200</v>
@@ -1583,25 +1583,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>549400</v>
+        <v>544200</v>
       </c>
       <c r="E17" s="3">
-        <v>592500</v>
+        <v>590300</v>
       </c>
       <c r="F17" s="3">
-        <v>335000</v>
+        <v>574100</v>
       </c>
       <c r="G17" s="3">
-        <v>648200</v>
+        <v>637700</v>
       </c>
       <c r="H17" s="3">
         <v>654300</v>
       </c>
       <c r="I17" s="3">
-        <v>653800</v>
+        <v>652200</v>
       </c>
       <c r="J17" s="3">
-        <v>595000</v>
+        <v>594600</v>
       </c>
       <c r="K17" s="3">
         <v>605500</v>
@@ -1684,25 +1684,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>30000</v>
+        <v>35200</v>
       </c>
       <c r="E18" s="3">
-        <v>24400</v>
+        <v>26600</v>
       </c>
       <c r="F18" s="3">
-        <v>251000</v>
+        <v>11900</v>
       </c>
       <c r="G18" s="3">
-        <v>45100</v>
+        <v>55600</v>
       </c>
       <c r="H18" s="3">
         <v>25700</v>
       </c>
       <c r="I18" s="3">
-        <v>27400</v>
+        <v>29000</v>
       </c>
       <c r="J18" s="3">
-        <v>-11500</v>
+        <v>-11100</v>
       </c>
       <c r="K18" s="3">
         <v>18000</v>
@@ -1821,26 +1821,26 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
@@ -1923,25 +1923,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>36400</v>
+        <v>35700</v>
       </c>
       <c r="E21" s="3">
-        <v>30900</v>
+        <v>27200</v>
       </c>
       <c r="F21" s="3">
-        <v>257500</v>
+        <v>12500</v>
       </c>
       <c r="G21" s="3">
-        <v>51600</v>
+        <v>56100</v>
       </c>
       <c r="H21" s="3">
-        <v>32000</v>
+        <v>26300</v>
       </c>
       <c r="I21" s="3">
-        <v>33900</v>
+        <v>29500</v>
       </c>
       <c r="J21" s="3">
-        <v>-4600</v>
+        <v>-9900</v>
       </c>
       <c r="K21" s="3">
         <v>24900</v>
@@ -2730,26 +2730,26 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -3033,26 +3033,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
@@ -4031,7 +4031,7 @@
         <v>26800</v>
       </c>
       <c r="G45" s="3">
-        <v>27700</v>
+        <v>6100</v>
       </c>
       <c r="H45" s="3">
         <v>41400</v>
@@ -4223,26 +4223,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -5207,25 +5207,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5308,25 +5308,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>296700</v>
+        <v>289400</v>
       </c>
       <c r="E59" s="3">
-        <v>328300</v>
+        <v>321500</v>
       </c>
       <c r="F59" s="3">
-        <v>568300</v>
+        <v>561100</v>
       </c>
       <c r="G59" s="3">
-        <v>348900</v>
+        <v>265000</v>
       </c>
       <c r="H59" s="3">
-        <v>355600</v>
+        <v>347800</v>
       </c>
       <c r="I59" s="3">
-        <v>349800</v>
+        <v>342300</v>
       </c>
       <c r="J59" s="3">
-        <v>335500</v>
+        <v>328700</v>
       </c>
       <c r="K59" s="3">
         <v>363500</v>
@@ -5510,25 +5510,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>215000</v>
+        <v>241800</v>
       </c>
       <c r="E61" s="3">
-        <v>220000</v>
+        <v>246600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="G61" s="3">
-        <v>150000</v>
+        <v>180000</v>
       </c>
       <c r="H61" s="3">
-        <v>179000</v>
+        <v>209400</v>
       </c>
       <c r="I61" s="3">
-        <v>230000</v>
+        <v>259600</v>
       </c>
       <c r="J61" s="3">
-        <v>250000</v>
+        <v>271600</v>
       </c>
       <c r="K61" s="3">
         <v>230000</v>
@@ -5611,25 +5611,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>231800</v>
+        <v>36900</v>
       </c>
       <c r="E62" s="3">
-        <v>212200</v>
+        <v>25800</v>
       </c>
       <c r="F62" s="3">
-        <v>191700</v>
+        <v>25600</v>
       </c>
       <c r="G62" s="3">
-        <v>205200</v>
+        <v>24100</v>
       </c>
       <c r="H62" s="3">
-        <v>183600</v>
+        <v>22400</v>
       </c>
       <c r="I62" s="3">
-        <v>173700</v>
+        <v>21400</v>
       </c>
       <c r="J62" s="3">
-        <v>188300</v>
+        <v>20800</v>
       </c>
       <c r="K62" s="3">
         <v>130900</v>
@@ -7407,25 +7407,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6400</v>
+        <v>5700</v>
       </c>
       <c r="E83" s="3">
-        <v>6500</v>
+        <v>5500</v>
       </c>
       <c r="F83" s="3">
-        <v>6500</v>
+        <v>5500</v>
       </c>
       <c r="G83" s="3">
-        <v>6500</v>
+        <v>3400</v>
       </c>
       <c r="H83" s="3">
-        <v>6300</v>
+        <v>5600</v>
       </c>
       <c r="I83" s="3">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="J83" s="3">
-        <v>6900</v>
+        <v>7200</v>
       </c>
       <c r="K83" s="3">
         <v>7100</v>
@@ -8592,25 +8592,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3100</v>
+        <v>181200</v>
       </c>
       <c r="E96" s="3">
-        <v>-182400</v>
+        <v>4300</v>
       </c>
       <c r="F96" s="3">
-        <v>-3100</v>
+        <v>3100</v>
       </c>
       <c r="G96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="J96" s="3">
-        <v>-3100</v>
+        <v>3100</v>
       </c>
       <c r="K96" s="3">
         <v>-3000</v>
@@ -9096,26 +9096,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>REVG</t>
   </si>
@@ -656,454 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>525100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>597900</v>
+      </c>
+      <c r="F8" s="3">
         <v>579400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>616900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>586000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>693300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>680000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>681200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>583500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>623500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>594800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>576300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>537000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>589900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>593300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>643600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>554000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>616300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>582200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>547000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>532100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>652900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>617000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>615000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>518700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>659900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>597700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>608900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>514900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>683900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>595600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>545300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>442900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>544800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>455300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>519100</v>
+      </c>
+      <c r="F9" s="3">
         <v>501100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>539600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>523100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>597800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>599800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>598700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>525600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>556700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>527000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>519200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>481200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>524600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>516700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>556200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>492300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>554500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>515700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>494600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>484700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>591200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>545700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>542600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>472400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>586700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>518200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>536100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>462300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>587700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>517600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>472500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>395400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>78800</v>
+      </c>
+      <c r="F10" s="3">
         <v>78300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>77300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>62900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>95500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>80200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>82500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>57900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>66800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>67800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>57100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>55800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>65300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>76600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>87400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>61700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>61800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>66500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>52400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>47400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>61700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>71300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>72400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>46300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>73200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>79500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>72800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>52600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>96200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>78000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>72800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>47500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1165,117 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>24</v>
+      <c r="E12" s="3">
+        <v>3300</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="3">
-        <v>-3500</v>
+      <c r="G12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>24</v>
+      <c r="I12" s="3">
+        <v>4700</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="3">
         <v>1300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="W12" s="3">
-        <v>1100</v>
       </c>
       <c r="X12" s="3">
         <v>1200</v>
       </c>
       <c r="Y12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z12" s="3">
         <v>1200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB12" s="3">
         <v>1300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>900</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>1000</v>
       </c>
       <c r="AH12" s="3">
         <v>1200</v>
       </c>
       <c r="AI12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AK12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,210 +1375,228 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="F14" s="3">
         <v>5200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-239100</v>
       </c>
-      <c r="G14" s="3">
-        <v>10500</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>2300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>3700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>5200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>17400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>8300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>3000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>7600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>1900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>3800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>35900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>1900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>4100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>2300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>12300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
         <v>600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>500</v>
       </c>
       <c r="H15" s="3">
         <v>600</v>
       </c>
       <c r="I15" s="3">
+        <v>500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>600</v>
+      </c>
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>2300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>2600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>3000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>3400</v>
-      </c>
-      <c r="V15" s="3">
-        <v>4000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>4000</v>
       </c>
       <c r="X15" s="3">
         <v>4000</v>
       </c>
       <c r="Y15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>4600</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>4600</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>4500</v>
       </c>
       <c r="AB15" s="3">
         <v>4600</v>
       </c>
       <c r="AC15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AE15" s="3">
         <v>4300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>4700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>4500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>5100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>2700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>2600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>497100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>560200</v>
+      </c>
+      <c r="F17" s="3">
         <v>544200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>590300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>574100</v>
       </c>
-      <c r="G17" s="3">
-        <v>637700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>648200</v>
+      </c>
+      <c r="J17" s="3">
         <v>654300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>652200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>594600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>605500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>577600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>575500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>536100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>579100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>563800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>610300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>548500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>623500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>580600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>557400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>536800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>657900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>601100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>598900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>529900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>678300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>568800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>592500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>513900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>642700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>566800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>531000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>456600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>518500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>37700</v>
+      </c>
+      <c r="F18" s="3">
         <v>35200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>26600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>11900</v>
       </c>
-      <c r="G18" s="3">
-        <v>55600</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>45100</v>
+      </c>
+      <c r="J18" s="3">
         <v>25700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>29000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-11100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>18000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>17200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>10800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>29500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>33300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>5500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-7200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-10400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-5000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>15900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>16100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-18400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>28900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>16400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>41200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>28800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>14300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-13700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,8 +1882,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1837,32 +1905,32 @@
         <v>24</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-6200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1917,412 +1985,442 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>38200</v>
+      </c>
+      <c r="F21" s="3">
         <v>35700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>27200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>12500</v>
       </c>
-      <c r="G21" s="3">
-        <v>56100</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>45600</v>
+      </c>
+      <c r="J21" s="3">
         <v>26300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>29500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-9900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>24900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>24100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>9500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>10500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>12400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>37000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>41400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>14100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>10800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>6100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>26900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>27500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>40700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>27500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>12000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>52300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>40400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>22200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F22" s="3">
         <v>7600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>6500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>6800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>6700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>7300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>7400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>7100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>4300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>3500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>2900</v>
       </c>
       <c r="P22" s="3">
         <v>3400</v>
       </c>
       <c r="Q22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S22" s="3">
         <v>5500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>5500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>5400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>5700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>7300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>8300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>8400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>8000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>7800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>7300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>6800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>6100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>5400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>5300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>4600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>3400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>7500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>17900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>244200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>38400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>18400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>20000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-18600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>12100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>12900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>26100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>27800</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-12600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-17700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-12000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-13300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>7500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>8100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-25700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>22100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>10300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>36000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>24300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>10900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F24" s="3">
         <v>4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>61500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>8700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>3500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-6600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-3500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>5900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>2900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>13300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>9100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>4100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F26" s="3">
         <v>18000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>15200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>182700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>29700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>14900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>14200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-13500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>8700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>23700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>20600</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-10200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-11100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-9400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-9800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>5600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>5600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-20900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>16200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>7400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>22700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>15200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>6800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F27" s="3">
         <v>18000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>15200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>182700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>29700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>14900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>14200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>8700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>23700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>20600</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-10200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-11100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-9400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>5600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>5600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-20900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>16200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>7400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>22700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>15200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>6800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2751,11 +2873,11 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -2763,32 +2885,32 @@
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
-        <v>4200</v>
+      <c r="O29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
+      <c r="Q29" s="3">
+        <v>4200</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>3500</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2799,23 +2921,23 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>2100</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>10400</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3162,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3049,32 +3189,32 @@
         <v>24</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>6200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3129,109 +3269,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F33" s="3">
         <v>18000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>15200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>182700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>29700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>14900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>14200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-13500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>8700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>23700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>20600</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-10200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-7600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-9400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>5600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>5600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>18300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>9400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>22700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>15200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>6800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F35" s="3">
         <v>18000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>15200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>182700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>29700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>14900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>14200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-13500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>8700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>23700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>20600</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-10200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-7600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-9400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>5600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>5600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>18300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>9400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>22700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>15200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>6800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3784,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F41" s="3">
         <v>50500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>38200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>87900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>21300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>20400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>13900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>13300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>11400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>17300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>21500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>67300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>19800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>6500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>13500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>11900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>14700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>13200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>12700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>17800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>14100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>14000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>15100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,412 +3994,442 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>152300</v>
+      </c>
+      <c r="F43" s="3">
         <v>201400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>210600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>223500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>226500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>210600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>239500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>218800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>215000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>224300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>222200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>249800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>213300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>198700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>231100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>207700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>229300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>239300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>217200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>230500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>253500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>236200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>281500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>225000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>266900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>232800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>251700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>224200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>243200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>243400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>223300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>188000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>181200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>601800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>602800</v>
+      </c>
+      <c r="F44" s="3">
         <v>632300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>630400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>650400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>657700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>644000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>654400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>671900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>629500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>599300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>562900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>527600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>481700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>519700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>532900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>533200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>537200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>572300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>594000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>532700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>513400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>557900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>536300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>529800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>514000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>531500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>483900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>486700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>452400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>457800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>417600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>341500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>325600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="3">
         <v>30200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>26000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>26800</v>
       </c>
-      <c r="G45" s="3">
-        <v>6100</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="3">
         <v>41400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>21500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>27600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>23500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>38000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>33600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>25600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>52700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>46700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>38400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>27300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>34100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>57900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>91100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>22900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>38900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>51300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>40300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>45300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>50300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>24200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>14700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>14100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>13400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>14900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>18300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>16400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>840300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>806500</v>
+      </c>
+      <c r="F46" s="3">
         <v>914400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>905200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>988600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>933200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>907000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>924400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>941300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>888400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>876400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>824600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>816900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>761000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>774300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>810100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>777300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>812000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>886800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>923800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>853400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>809100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>865200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>864600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>813600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>843100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>803200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>763500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>737700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>726800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>730200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>673300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>561000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>529700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,11 +4454,11 @@
       <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4319,210 +4529,228 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>159900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>162300</v>
+      </c>
+      <c r="F48" s="3">
         <v>180500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>182800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>188100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>196500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>190600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>184900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>175400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>169100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>166800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>167000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>177300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>176700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>171000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>172800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>175500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>191600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>207000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>220600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>220400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>201700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>203200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>206500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>214000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>214300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>241100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>238800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>227600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>217100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>207600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>198200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>161900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>146400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>232500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>233100</v>
+      </c>
+      <c r="F49" s="3">
         <v>233600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>236000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>237700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>273000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>273500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>274100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>275100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>276500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>277800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>279200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>281200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>283600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>286000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>288400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>290900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>293400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>299600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>302500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>315700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>319700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>323700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>327500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>332000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>336400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>342500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>346700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>349900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>301100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>300300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>295500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>215500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>8400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>9100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>9800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>10600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>11200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>15000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>16900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>17000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>21600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>21600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>15400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>15300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>16000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>16000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>16500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>16600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>14000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>14700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>15000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>14300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>16300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>9700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>9400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>9400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>8000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>8500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>3900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1242100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1213000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1334700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1330400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1421100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1410400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1379500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1392500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1401600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1344600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1332200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1285800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1292300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1238300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1252900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1292900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1259100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1312300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1409400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1462900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1406000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1347100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1406100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1413300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1374600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1408100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1358700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1324500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1254400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1246100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1175400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>942200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>889000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5360,117 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>169800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>188800</v>
+      </c>
+      <c r="F57" s="3">
         <v>196600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>190200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>165000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>208300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>192700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>185700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>187100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>163900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>159200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>144700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>137100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>116200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>129600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>137200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>128700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>169500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>175800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>193200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>187400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>200800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>211000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>196500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>163900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>218100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>167200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>188100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>144300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>217300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>170200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>140600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>111400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,29 +5478,29 @@
         <v>7300</v>
       </c>
       <c r="E58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G58" s="3">
         <v>6800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>7200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5249,10 +5517,10 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>1700</v>
@@ -5261,31 +5529,31 @@
         <v>1700</v>
       </c>
       <c r="V58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X58" s="3">
         <v>3400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1800</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>1300</v>
       </c>
       <c r="AB58" s="3">
         <v>1300</v>
       </c>
       <c r="AC58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="AD58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="AE58" s="3">
         <v>800</v>
@@ -5296,418 +5564,448 @@
       <c r="AG58" s="3">
         <v>800</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AH58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>234200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>239500</v>
+      </c>
+      <c r="F59" s="3">
         <v>289400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>321500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>561100</v>
       </c>
-      <c r="G59" s="3">
-        <v>265000</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>294200</v>
+      </c>
+      <c r="J59" s="3">
         <v>347800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>342300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>328700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>363500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>415500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>372500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>348300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>320800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>304400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>301800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>272700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>276100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>291300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>280300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>217100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>231600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>221700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>202000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>185900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>197800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>186500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>184500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>191300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>192100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>187800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>185500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>182800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>202100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>469300</v>
+      </c>
+      <c r="F60" s="3">
         <v>493300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>518500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>733300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>557200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>548300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>535500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>522600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>527400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>574700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>517200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>485400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>437000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>434000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>439000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>403100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>447300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>468800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>475200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>407900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>436000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>434500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>400300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>351100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>417200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>355000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>373400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>336400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>410100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>358800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>326900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>294200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>331600</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>164100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>110700</v>
+      </c>
+      <c r="F61" s="3">
         <v>241800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>246600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>28400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>180000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>209400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>259600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>271600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>230000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>250000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>243000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>256000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>215000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>250000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>306000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>330400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>340500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>388700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>440800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>458300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>376600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>416800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>460000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>470400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>420600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>440400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>368900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>371500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>229100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>299400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>280800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>336000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>37800</v>
+      </c>
+      <c r="F62" s="3">
         <v>36900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>25800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>25600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>24100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>22400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>21400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>20800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>130900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>59500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>62100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>62800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>67500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>47400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>49100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>50300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>52200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>69800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>62000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>43900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>29300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>37300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>36700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>37000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>37900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>44300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>35000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>35100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>42800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>40200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>32400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>34200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>813300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>777900</v>
+      </c>
+      <c r="F66" s="3">
         <v>940100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>950700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>925000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>912400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>910900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>939200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>960900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>888300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>884200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>822300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>804200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>719500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>731400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>794100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>783800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>840000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>927300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>978000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>910100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>842100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>889600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>898000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>859500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>876700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>839700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>777300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>743000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>682000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>698300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>640000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>664400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>132600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>118300</v>
+      </c>
+      <c r="F72" s="3">
         <v>80000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>65100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>53000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>52700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>26000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>14100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>19500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>13800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>12700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>16700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>19900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-21100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-21100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-11200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-7600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>15800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>27600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>25200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>22800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>40600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>65900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>50700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>46600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>40400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>20900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>8900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>5300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>428800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>435100</v>
+      </c>
+      <c r="F76" s="3">
         <v>394600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>379700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>496100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>498000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>468600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>453300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>440700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>456300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>448000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>463500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>488100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>518800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>521500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>498800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>475300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>472300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>482100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>484900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>495900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>505000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>516500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>515300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>515100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>531400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>563400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>581400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>581600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>572400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>547700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>535400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>277800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F81" s="3">
         <v>18000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>15200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>182700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>29700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>14900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>14200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-13500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>8700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>23700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>20600</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-10200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-7600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-9400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>5600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>5600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>18300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>9400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>22700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>15200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>6800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7797,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F83" s="3">
         <v>5700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>5500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>6700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>7200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>6900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>8700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>9600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>7800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>7500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>8100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>8600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>9300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>9200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>10900</v>
-      </c>
-      <c r="V83" s="3">
-        <v>10800</v>
       </c>
       <c r="W83" s="3">
         <v>10900</v>
       </c>
       <c r="X83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Z83" s="3">
         <v>11000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>11400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>12400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>12100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>11800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>11100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>11000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>11000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>11500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>7900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>7400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>68600</v>
+      </c>
+      <c r="F89" s="3">
         <v>14400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>40100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-69700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>53100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>65200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>15100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>32100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>32100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>31100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>57700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>63500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>35200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>30700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>35300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-13300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>30500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>61200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-39400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>37600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>28500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-72400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>93200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-25100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>86800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8585,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-5900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-10500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-13100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-9100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-7400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-10800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2900</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>2100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8902,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>4200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>297700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-11900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-9100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-4400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>7100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>11900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>48300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-57200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-5300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>11900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-14400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-38300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-16800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,53 +9052,55 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="3">
         <v>181200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>4300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>3100</v>
-      </c>
-      <c r="G96" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>3000</v>
       </c>
       <c r="I96" s="3">
         <v>3000</v>
       </c>
       <c r="J96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L96" s="3">
         <v>3100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-3000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-3000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-3100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-3300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-3300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8640,46 +9108,46 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-3100</v>
       </c>
       <c r="X96" s="3">
         <v>-3100</v>
       </c>
       <c r="Y96" s="3">
-        <v>-3200</v>
+        <v>-3100</v>
       </c>
       <c r="Z96" s="3">
         <v>-3100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AE96" s="3">
         <v>-3200</v>
       </c>
       <c r="AF96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AG96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
@@ -8687,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,109 +9476,121 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-141200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-94000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-161400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-30900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-54100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-23200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>12500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-23000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-17800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-37600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>8700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-42800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-59300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-32800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-11300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-48500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-55500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-23900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>78600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-41700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-48700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-19100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>48200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-29900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>34400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>140200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>15700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>182300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>76300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-76400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,11 +9615,11 @@
       <c r="J101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9192,105 +9690,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="F102" s="3">
         <v>12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-49700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>66600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-14000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>5600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-8000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-5900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-4200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-45800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>64000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-16500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>13300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-7000</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-2800</v>
       </c>
       <c r="AB102" s="3">
         <v>1600</v>
       </c>
       <c r="AC102" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>3700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>4300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REVG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>REVG</t>
   </si>
@@ -656,480 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>629100</v>
+      </c>
+      <c r="E8" s="3">
         <v>525100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>597900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>579400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>616900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>586000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>693300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>680000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>681200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>583500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>623500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>594800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>576300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>537000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>589900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>593300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>643600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>554000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>616300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>582200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>547000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>532100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>652900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>617000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>615000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>518700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>659900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>597700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>608900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>514900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>683900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>595600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>545300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>442900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>544800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>533400</v>
+      </c>
+      <c r="E9" s="3">
         <v>455300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>519100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>501100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>539600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>523100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>597800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>599800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>598700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>525600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>556700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>527000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>519200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>481200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>524600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>516700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>556200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>492300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>554500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>515700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>494600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>484700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>591200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>545700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>542600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>472400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>586700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>518200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>536100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>462300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>587700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>517600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>472500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>395400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E10" s="3">
         <v>69800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>78800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>77300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>62900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>95500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>80200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>82500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>57900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>67800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>57100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>65300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>76600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>87400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>61700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>61800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>66500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>52400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>47400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>61700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>71300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>72400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>46300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>73200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>79500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>72800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>52600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>96200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>78000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>72800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>47500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,19 +1179,20 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3">
         <v>3300</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
@@ -1187,11 +1200,11 @@
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3">
         <v>4700</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>24</v>
@@ -1199,83 +1212,86 @@
       <c r="L12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>1200</v>
       </c>
       <c r="AA12" s="3">
         <v>1200</v>
       </c>
       <c r="AB12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC12" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>1600</v>
       </c>
       <c r="AD12" s="3">
         <v>1600</v>
       </c>
       <c r="AE12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AF12" s="3">
         <v>1500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1381,180 +1397,186 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-25800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5200</v>
       </c>
-      <c r="G14" s="3">
-        <v>2200</v>
-      </c>
       <c r="H14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I14" s="3">
         <v>-239100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>35900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>12300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>500</v>
       </c>
       <c r="G15" s="3">
+        <v>500</v>
+      </c>
+      <c r="H15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
+        <v>500</v>
+      </c>
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3">
-        <v>500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1400</v>
       </c>
       <c r="M15" s="3">
         <v>1400</v>
       </c>
       <c r="N15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O15" s="3">
         <v>1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2400</v>
       </c>
       <c r="Q15" s="3">
         <v>2400</v>
       </c>
       <c r="R15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S15" s="3">
         <v>2300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3400</v>
-      </c>
-      <c r="X15" s="3">
-        <v>4000</v>
       </c>
       <c r="Y15" s="3">
         <v>4000</v>
@@ -1563,40 +1585,43 @@
         <v>4000</v>
       </c>
       <c r="AA15" s="3">
-        <v>4600</v>
+        <v>4000</v>
       </c>
       <c r="AB15" s="3">
         <v>4600</v>
       </c>
       <c r="AC15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AD15" s="3">
         <v>4500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>2600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>579400</v>
+      </c>
+      <c r="E17" s="3">
         <v>497100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>560200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>544200</v>
       </c>
-      <c r="G17" s="3">
-        <v>590300</v>
-      </c>
       <c r="H17" s="3">
+        <v>588900</v>
+      </c>
+      <c r="I17" s="3">
         <v>574100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>648200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>654300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>652200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>594600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>605500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>577600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>575500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>536100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>579100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>563800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>610300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>548500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>623500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>580600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>557400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>536800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>657900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>601100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>598900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>529900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>678300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>568800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>592500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>513900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>642700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>566800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>531000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>456600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>518500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E18" s="3">
         <v>28000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>35200</v>
       </c>
-      <c r="G18" s="3">
-        <v>26600</v>
-      </c>
       <c r="H18" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I18" s="3">
         <v>11900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>29000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>29500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>33300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-18400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>28900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>41200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>28800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-13700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1884,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1904,24 +1937,24 @@
       <c r="H20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1929,11 +1962,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-6200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1991,436 +2024,451 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E21" s="3">
         <v>28600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>38200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35700</v>
       </c>
-      <c r="G21" s="3">
-        <v>27200</v>
-      </c>
       <c r="H21" s="3">
+        <v>34500</v>
+      </c>
+      <c r="I21" s="3">
         <v>12500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>26900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>40700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>27500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>12000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>52300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>40400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E22" s="3">
         <v>6000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3400</v>
-      </c>
-      <c r="S22" s="3">
-        <v>5500</v>
       </c>
       <c r="T22" s="3">
         <v>5500</v>
       </c>
       <c r="U22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="V22" s="3">
         <v>5400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5700</v>
-      </c>
-      <c r="W22" s="3">
-        <v>7300</v>
       </c>
       <c r="X22" s="3">
         <v>7300</v>
       </c>
       <c r="Y22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>8300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E23" s="3">
         <v>22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>56000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>244200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>38400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27800</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-12600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>22100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>36000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>24300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E24" s="3">
         <v>3800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>3400</v>
       </c>
       <c r="N24" s="3">
         <v>3400</v>
       </c>
       <c r="O24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-6600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>9100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E26" s="3">
         <v>18200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>182700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20600</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9800</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>5600</v>
       </c>
       <c r="AA26" s="3">
         <v>5600</v>
       </c>
       <c r="AB26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-20900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E27" s="3">
         <v>18200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>182700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20600</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-10200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>5600</v>
       </c>
       <c r="AA27" s="3">
         <v>5600</v>
       </c>
       <c r="AB27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-20900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>22700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2879,8 +2939,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
@@ -2891,11 +2951,11 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3">
         <v>4200</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
@@ -2903,17 +2963,17 @@
       <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>3500</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -2927,20 +2987,20 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>2100</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>10400</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3188,24 +3257,24 @@
       <c r="H32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3213,11 +3282,11 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>6200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3275,115 +3344,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E33" s="3">
         <v>18200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>182700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>23700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>20600</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-10200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>5600</v>
       </c>
       <c r="AA33" s="3">
         <v>5600</v>
       </c>
       <c r="AB33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>22700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>15200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E35" s="3">
         <v>18200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>182700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>23700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>20600</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-10200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>5600</v>
       </c>
       <c r="AA35" s="3">
         <v>5600</v>
       </c>
       <c r="AB35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>22700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>15200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E41" s="3">
         <v>31600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>50500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>87900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>67300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>14700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>17800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>15100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,436 +4089,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E43" s="3">
         <v>185300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>152300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>201400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>210600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>223500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>226500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>210600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>239500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>218800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>215000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>224300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>222200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>249800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>213300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>198700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>231100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>207700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>229300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>239300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>217200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>230500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>253500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>236200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>281500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>225000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>266900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>232800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>251700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>224200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>243200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>243400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>223300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>188000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>181200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>565700</v>
+      </c>
+      <c r="E44" s="3">
         <v>601800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>602800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>632300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>630400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>650400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>657700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>644000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>654400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>671900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>629500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>599300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>562900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>527600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>481700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>519700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>532900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>533200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>537200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>572300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>594000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>532700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>513400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>557900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>536300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>529800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>514000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>531500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>483900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>486700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>452400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>457800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>417600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>341500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>325600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E45" s="3">
         <v>21600</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26800</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>41400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>52700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>46700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>57900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>91100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>38900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>51300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>45300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>50300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>14700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>14100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>13400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>14900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>16400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>831700</v>
+      </c>
+      <c r="E46" s="3">
         <v>840300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>806500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>914400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>905200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>988600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>933200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>907000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>924400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>941300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>888400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>876400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>824600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>816900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>761000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>774300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>810100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>777300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>812000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>886800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>923800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>853400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>809100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>865200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>864600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>813600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>843100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>803200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>763500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>737700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>726800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>730200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>673300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>561000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>529700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4460,8 +4564,8 @@
       <c r="L47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4535,222 +4639,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E48" s="3">
         <v>159900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>162300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>180500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>182800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>188100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>196500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>190600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>184900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>175400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>169100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>166800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>167000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>177300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>176700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>171000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>175500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>191600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>207000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>220600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>220400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>201700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>203200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>206500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>214000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>214300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>241100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>238800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>227600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>217100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>207600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>198200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>161900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>146400</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>223300</v>
+      </c>
+      <c r="E49" s="3">
         <v>232500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>233100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>233600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>236000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>237700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>273000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>273500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>274100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>275100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>276500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>277800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>279200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>281200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>283600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>286000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>288400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>290900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>293400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>299600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>302500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>315700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>319700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>323700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>327500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>332000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>336400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>342500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>346700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>349900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>301100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>300300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>295500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>215500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5700</v>
+        <v>8100</v>
       </c>
       <c r="E52" s="3">
         <v>5700</v>
       </c>
       <c r="F52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G52" s="3">
         <v>6200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>21600</v>
       </c>
       <c r="S52" s="3">
         <v>21600</v>
       </c>
       <c r="T52" s="3">
+        <v>21600</v>
+      </c>
+      <c r="U52" s="3">
         <v>15400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15300</v>
-      </c>
-      <c r="V52" s="3">
-        <v>16000</v>
       </c>
       <c r="W52" s="3">
         <v>16000</v>
       </c>
       <c r="X52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Y52" s="3">
         <v>16500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>15000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9700</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>9400</v>
       </c>
       <c r="AG52" s="3">
         <v>9400</v>
       </c>
       <c r="AH52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AI52" s="3">
         <v>8000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1227600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1242100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1213000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1334700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1330400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1421100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1410400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1379500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1392500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1401600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1344600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1332200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1285800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1292300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1238300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1252900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1292900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1259100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1312300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1409400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1462900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1406000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1347100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1406100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1413300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1374600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1408100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1358700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1324500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1254400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1246100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1175400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>942200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>889000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,120 +5491,124 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>221800</v>
+      </c>
+      <c r="E57" s="3">
         <v>169800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>188800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>196600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>190200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>165000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>208300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>192700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>185700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>187100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>163900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>159200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>144700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>137100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>116200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>129600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>137200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>128700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>169500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>175800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>193200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>187400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>211000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>196500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>163900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>218100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>167200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>188100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>144300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>217300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>170200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>140600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>111400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7300</v>
+        <v>5700</v>
       </c>
       <c r="E58" s="3">
         <v>7300</v>
@@ -5484,26 +5617,26 @@
         <v>7300</v>
       </c>
       <c r="G58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H58" s="3">
         <v>6800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5523,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>1700</v>
@@ -5535,19 +5668,19 @@
         <v>1700</v>
       </c>
       <c r="X58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y58" s="3">
         <v>3400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3600</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>1800</v>
       </c>
       <c r="AA58" s="3">
         <v>1800</v>
       </c>
       <c r="AB58" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="AC58" s="3">
         <v>1300</v>
@@ -5556,7 +5689,7 @@
         <v>1300</v>
       </c>
       <c r="AE58" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="AF58" s="3">
         <v>800</v>
@@ -5570,442 +5703,457 @@
       <c r="AI58" s="3">
         <v>800</v>
       </c>
-      <c r="AJ58" s="3" t="s">
+      <c r="AJ58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AK58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E59" s="3">
         <v>234200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>239500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>289400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>321500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>561100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>294200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>347800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>342300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>328700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>363500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>415500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>372500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>348300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>320800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>304400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>301800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>272700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>276100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>291300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>280300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>217100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>231600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>221700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>202000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>185900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>197800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>186500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>184500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>191300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>192100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>187800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>185500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>182800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>202100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500400</v>
+      </c>
+      <c r="E60" s="3">
         <v>434700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>469300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>493300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>518500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>733300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>557200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>548300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>535500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>522600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>527400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>574700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>517200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>485400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>437000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>434000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>439000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>403100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>447300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>468800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>475200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>407900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>436000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>434500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>400300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>351100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>417200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>355000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>373400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>336400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>410100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>358800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>326900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>294200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>331600</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E61" s="3">
         <v>164100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>110700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>241800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>246600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>180000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>209400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>259600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>271600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>230000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>250000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>243000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>256000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>215000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>250000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>306000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>330400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>340500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>388700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>440800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>458300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>376600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>416800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>460000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>470400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>420600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>440400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>368900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>371500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>229100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>299400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>336000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E62" s="3">
         <v>39800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>130900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>62100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>62800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>67500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>49100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>50300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>52200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>69800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>62000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>43900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>29300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>36700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>37000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>37900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>44300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>35000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>35100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>42800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>40200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>34200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>869800</v>
+      </c>
+      <c r="E66" s="3">
         <v>813300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>777900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>940100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>950700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>925000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>912400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>910900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>939200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>960900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>888300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>884200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>822300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>804200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>719500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>731400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>794100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>783800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>840000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>927300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>978000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>910100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>842100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>889600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>898000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>859500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>876700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>839700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>777300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>743000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>682000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>698300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>640000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>664400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E72" s="3">
         <v>132600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>118300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>80000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>65100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-500</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-21100</v>
       </c>
       <c r="U72" s="3">
         <v>-21100</v>
       </c>
       <c r="V72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="W72" s="3">
         <v>-11200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>40600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>65900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>50700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>46600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>40400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>20900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>357800</v>
+      </c>
+      <c r="E76" s="3">
         <v>428800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>435100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>394600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>379700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>496100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>498000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>468600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>453300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>440700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>456300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>448000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>463500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>488100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>518800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>521500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>498800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>475300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>472300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>482100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>484900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>495900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>505000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>516500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>515300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>515100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>531400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>563400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>581400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>581600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>572400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>547700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>535400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>277800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E81" s="3">
         <v>18200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>182700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>23700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>20600</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-10200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>5600</v>
       </c>
       <c r="AA81" s="3">
         <v>5600</v>
       </c>
       <c r="AB81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>22700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>15200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7808,106 +8006,109 @@
         <v>5900</v>
       </c>
       <c r="E83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>5500</v>
       </c>
       <c r="H83" s="3">
         <v>5500</v>
       </c>
       <c r="I83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>11800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11100</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>11000</v>
       </c>
       <c r="AG83" s="3">
         <v>11000</v>
       </c>
       <c r="AH83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AI83" s="3">
         <v>11500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>7400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>68600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-69700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>32100</v>
       </c>
       <c r="N89" s="3">
         <v>32100</v>
       </c>
       <c r="O89" s="3">
+        <v>32100</v>
+      </c>
+      <c r="P89" s="3">
         <v>31100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>57700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>63500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>35300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>30500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>61200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-39400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>37600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>28500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-72400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>93200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-25100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>86800</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,77 +8806,78 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-5900</v>
       </c>
       <c r="G91" s="3">
         <v>-5900</v>
       </c>
       <c r="H91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-10500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2900</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -8665,37 +8885,40 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>2100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>46700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>297700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>11900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>48300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>11900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-14400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-38300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-16800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,28 +9286,29 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E96" s="3">
         <v>3900</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="F96" s="3">
-        <v>181200</v>
+        <v>3400</v>
       </c>
       <c r="G96" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H96" s="3">
         <v>4300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3100</v>
-      </c>
-      <c r="I96" s="3">
-        <v>3000</v>
       </c>
       <c r="J96" s="3">
         <v>3000</v>
@@ -9084,25 +9317,25 @@
         <v>3000</v>
       </c>
       <c r="L96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M96" s="3">
         <v>3100</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-3000</v>
       </c>
       <c r="N96" s="3">
         <v>-3000</v>
       </c>
       <c r="O96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-3300</v>
       </c>
       <c r="Q96" s="3">
         <v>-3300</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -9114,13 +9347,13 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>-3200</v>
       </c>
       <c r="X96" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="Y96" s="3">
         <v>-3100</v>
@@ -9129,19 +9362,19 @@
         <v>-3100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC96" s="3">
         <v>-3100</v>
       </c>
       <c r="AD96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AF96" s="3">
         <v>-3200</v>
@@ -9150,7 +9383,7 @@
         <v>-3200</v>
       </c>
       <c r="AH96" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,115 +9724,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-108700</v>
+      </c>
+      <c r="E100" s="3">
         <v>24900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-141200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-94000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-161400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-54100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-23200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-37600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-42800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-59300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-32800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-48500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-55500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>78600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-41700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>48200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-29900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>34400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>140200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>15700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>182300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>76300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-76400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9621,8 +9869,8 @@
       <c r="L101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9696,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>7000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-49700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-45800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>64000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-6400</v>
       </c>
     </row>
